--- a/artfynd/A 24273-2026 artfynd.xlsx
+++ b/artfynd/A 24273-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>134058777</v>
       </c>
       <c r="B3" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24273-2026 artfynd.xlsx
+++ b/artfynd/A 24273-2026 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -790,38 +790,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134058777</v>
+        <v>134058776</v>
       </c>
       <c r="B3" t="n">
-        <v>110152</v>
+        <v>58308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>103008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604640</v>
+        <v>604615</v>
       </c>
       <c r="R3" t="n">
-        <v>6507865</v>
+        <v>6508037</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134058776</v>
+        <v>134058772</v>
       </c>
       <c r="B4" t="n">
-        <v>58308</v>
+        <v>58260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103008</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -948,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604615</v>
+        <v>604640</v>
       </c>
       <c r="R4" t="n">
-        <v>6508037</v>
+        <v>6507865</v>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134058772</v>
+        <v>134058777</v>
       </c>
       <c r="B5" t="n">
-        <v>58260</v>
+        <v>110159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,35 +1039,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>6507865</v>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 24273-2026 artfynd.xlsx
+++ b/artfynd/A 24273-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134058769</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134058776</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134058772</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,8 +1156,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134058777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>